--- a/database/lojas e senhas.xlsx
+++ b/database/lojas e senhas.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\TeleFluxo_Instalador\database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D5E5C17-73E3-4D7E-B469-3A81BECB2CA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF499FCA-019A-4EDD-8DE3-FFDD4B2EA75B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DC387A1A-0365-4EFE-8541-627FD66421E4}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="86">
   <si>
     <t>OPERAÇÃO</t>
   </si>
@@ -412,7 +412,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -436,6 +436,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -855,7 +861,7 @@
       <c r="C5" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E5" s="3">
@@ -864,6 +870,9 @@
       <c r="F5" s="5" t="s">
         <v>81</v>
       </c>
+      <c r="H5" s="10" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
@@ -875,7 +884,7 @@
       <c r="C6" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="8" t="s">
         <v>15</v>
       </c>
       <c r="E6" s="3">
@@ -884,6 +893,9 @@
       <c r="F6" s="5" t="s">
         <v>81</v>
       </c>
+      <c r="H6" s="11" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
@@ -955,7 +967,7 @@
       <c r="C10" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="8" t="s">
         <v>23</v>
       </c>
       <c r="E10" s="3">
@@ -963,6 +975,9 @@
       </c>
       <c r="F10" s="5" t="s">
         <v>81</v>
+      </c>
+      <c r="H10" s="10" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -1306,6 +1321,9 @@
   </sheetData>
   <hyperlinks>
     <hyperlink ref="D23" r:id="rId1" xr:uid="{637C8505-8BF2-42A3-9079-B16B29588BD3}"/>
+    <hyperlink ref="D5" r:id="rId2" xr:uid="{A8E57DDA-46F9-43FB-805C-3EDEAC64B78C}"/>
+    <hyperlink ref="D6" r:id="rId3" xr:uid="{87B8274B-BC10-448C-AF1F-7040968FF2C3}"/>
+    <hyperlink ref="D10" r:id="rId4" xr:uid="{44615FFD-2BCE-4CD9-9EBE-B0832EF9B8B3}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/database/lojas e senhas.xlsx
+++ b/database/lojas e senhas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\TeleFluxo_Instalador\database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF499FCA-019A-4EDD-8DE3-FFDD4B2EA75B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B79FBF8-9A16-4B7E-9978-5C2339763BDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DC387A1A-0365-4EFE-8541-627FD66421E4}"/>
   </bookViews>
@@ -412,7 +412,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -437,12 +437,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -870,7 +864,7 @@
       <c r="F5" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="H5" s="10" t="s">
+      <c r="H5" s="7" t="s">
         <v>84</v>
       </c>
     </row>
@@ -893,7 +887,7 @@
       <c r="F6" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="H6" s="11" t="s">
+      <c r="H6" s="9" t="s">
         <v>84</v>
       </c>
     </row>
@@ -976,7 +970,7 @@
       <c r="F10" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="H10" s="10" t="s">
+      <c r="H10" s="7" t="s">
         <v>85</v>
       </c>
     </row>

--- a/database/lojas e senhas.xlsx
+++ b/database/lojas e senhas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\TeleFluxo_Instalador\database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B79FBF8-9A16-4B7E-9978-5C2339763BDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC757044-90EB-47E5-B47A-583237DFBB89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DC387A1A-0365-4EFE-8541-627FD66421E4}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="86">
   <si>
     <t>OPERAÇÃO</t>
   </si>
@@ -412,7 +412,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -437,6 +437,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -812,7 +815,7 @@
       <c r="C3" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="8" t="s">
         <v>9</v>
       </c>
       <c r="E3" s="3">
@@ -820,6 +823,9 @@
       </c>
       <c r="F3" s="5" t="s">
         <v>81</v>
+      </c>
+      <c r="H3" s="10" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1318,6 +1324,7 @@
     <hyperlink ref="D5" r:id="rId2" xr:uid="{A8E57DDA-46F9-43FB-805C-3EDEAC64B78C}"/>
     <hyperlink ref="D6" r:id="rId3" xr:uid="{87B8274B-BC10-448C-AF1F-7040968FF2C3}"/>
     <hyperlink ref="D10" r:id="rId4" xr:uid="{44615FFD-2BCE-4CD9-9EBE-B0832EF9B8B3}"/>
+    <hyperlink ref="D3" r:id="rId5" xr:uid="{0058E193-1179-4714-B8F4-C58785AC4EA2}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/database/lojas e senhas.xlsx
+++ b/database/lojas e senhas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\TeleFluxo_Instalador\database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC757044-90EB-47E5-B47A-583237DFBB89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E30C378-9F9D-4CE9-B2CE-B1D97D0BB0FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DC387A1A-0365-4EFE-8541-627FD66421E4}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="86">
   <si>
     <t>OPERAÇÃO</t>
   </si>
@@ -824,7 +824,7 @@
       <c r="F3" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="H3" s="10" t="s">
+      <c r="H3" s="7" t="s">
         <v>85</v>
       </c>
     </row>
@@ -1033,7 +1033,7 @@
       <c r="C13" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" s="8" t="s">
         <v>29</v>
       </c>
       <c r="E13" s="3">
@@ -1041,6 +1041,9 @@
       </c>
       <c r="F13" s="5" t="s">
         <v>81</v>
+      </c>
+      <c r="H13" s="10" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -1325,6 +1328,7 @@
     <hyperlink ref="D6" r:id="rId3" xr:uid="{87B8274B-BC10-448C-AF1F-7040968FF2C3}"/>
     <hyperlink ref="D10" r:id="rId4" xr:uid="{44615FFD-2BCE-4CD9-9EBE-B0832EF9B8B3}"/>
     <hyperlink ref="D3" r:id="rId5" xr:uid="{0058E193-1179-4714-B8F4-C58785AC4EA2}"/>
+    <hyperlink ref="D13" r:id="rId6" xr:uid="{12FF726A-C366-47EB-8171-88A5607AE470}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/database/lojas e senhas.xlsx
+++ b/database/lojas e senhas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\TeleFluxo_Instalador\database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E30C378-9F9D-4CE9-B2CE-B1D97D0BB0FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D2D62B0-19BA-4BED-AF64-159956C488BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DC387A1A-0365-4EFE-8541-627FD66421E4}"/>
+    <workbookView xWindow="2250" yWindow="2250" windowWidth="21600" windowHeight="11295" xr2:uid="{DC387A1A-0365-4EFE-8541-627FD66421E4}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha4" sheetId="1" r:id="rId1"/>
@@ -412,7 +412,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -437,9 +437,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1042,7 +1039,7 @@
       <c r="F13" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="H13" s="10" t="s">
+      <c r="H13" s="7" t="s">
         <v>85</v>
       </c>
     </row>
